--- a/data/trans_orig/P57B2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B2_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido feliz en 2023</t>
+          <t>Población según se ha sentido feliz en 2023 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225165</t>
+          <t>226003</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>270888</t>
+          <t>271724</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>206744</t>
+          <t>207962</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>243175</t>
+          <t>243965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>448558</t>
+          <t>444147</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>505936</t>
+          <t>503593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,99%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>175352</t>
+          <t>173173</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>217662</t>
+          <t>217951</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>156837</t>
+          <t>157384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191733</t>
+          <t>191820</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>340591</t>
+          <t>342943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>396045</t>
+          <t>401023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>42,2%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37365</t>
+          <t>37443</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65255</t>
+          <t>65080</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29651</t>
+          <t>29500</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48837</t>
+          <t>49970</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73251</t>
+          <t>72118</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>105572</t>
+          <t>105838</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18535</t>
+          <t>17467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30069</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>209329</t>
+          <t>208178</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>252013</t>
+          <t>252997</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>149670</t>
+          <t>151011</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182059</t>
+          <t>183526</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>369350</t>
+          <t>368926</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>424022</t>
+          <t>425134</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145958</t>
+          <t>147768</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>186055</t>
+          <t>189414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149285</t>
+          <t>148932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>182125</t>
+          <t>181424</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>306660</t>
+          <t>304312</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>358072</t>
+          <t>358335</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>35334</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63431</t>
+          <t>63044</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37382</t>
+          <t>37751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59912</t>
+          <t>59746</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78437</t>
+          <t>78357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112219</t>
+          <t>113546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>12609</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>18050</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>328591</t>
+          <t>329674</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>583769</t>
+          <t>586158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66362</t>
+          <t>66727</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87257</t>
+          <t>86139</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>402332</t>
+          <t>404717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>708217</t>
+          <t>710560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62613</t>
+          <t>60366</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>257173</t>
+          <t>256351</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50512</t>
+          <t>50550</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69946</t>
+          <t>69507</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>90006</t>
+          <t>90042</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>317082</t>
+          <t>314598</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69214</t>
+          <t>69145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34204</t>
+          <t>34768</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28408</t>
+          <t>24179</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100717</t>
+          <t>99961</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20204</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23897</t>
+          <t>24222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>452966</t>
+          <t>455331</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>526630</t>
+          <t>529479</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>411823</t>
+          <t>411773</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>734755</t>
+          <t>761897</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>903756</t>
+          <t>900893</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1325514</t>
+          <t>1366230</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>332632</t>
+          <t>330393</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>399763</t>
+          <t>396642</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>162635</t>
+          <t>153876</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>400151</t>
+          <t>397647</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>461004</t>
+          <t>451869</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>762410</t>
+          <t>766627</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>129465</t>
+          <t>132788</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>173490</t>
+          <t>176227</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63096</t>
+          <t>55260</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>149872</t>
+          <t>152840</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>185227</t>
+          <t>178296</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>308268</t>
+          <t>307347</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>41951</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23347</t>
+          <t>22430</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>24723</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>54860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174772</t>
+          <t>175020</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>220576</t>
+          <t>222915</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>191440</t>
+          <t>189673</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>289382</t>
+          <t>291674</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>365260</t>
+          <t>364220</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>496966</t>
+          <t>495333</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>149552</t>
+          <t>150974</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>194505</t>
+          <t>193395</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>339058</t>
+          <t>339272</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>513293</t>
+          <t>512034</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>504862</t>
+          <t>511208</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>714488</t>
+          <t>706963</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>53,91%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65774</t>
+          <t>65771</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>97517</t>
+          <t>97070</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>121258</t>
+          <t>126273</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>192827</t>
+          <t>192040</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>200113</t>
+          <t>199477</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>275501</t>
+          <t>275218</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14077</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32069</t>
+          <t>30766</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33594</t>
+          <t>33575</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>35189</t>
+          <t>33932</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>60466</t>
+          <t>59974</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>144546</t>
+          <t>146806</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>192726</t>
+          <t>191890</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>294178</t>
+          <t>296931</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>349518</t>
+          <t>351255</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>456286</t>
+          <t>457923</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>530958</t>
+          <t>533488</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,54%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41876</t>
+          <t>40339</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>89460</t>
+          <t>84778</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>268099</t>
+          <t>267766</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>318773</t>
+          <t>316720</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>320113</t>
+          <t>319582</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>390998</t>
+          <t>388007</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>109446</t>
+          <t>109392</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>141105</t>
+          <t>140003</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>112642</t>
+          <t>113259</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>149125</t>
+          <t>148502</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25552</t>
+          <t>26516</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>13373</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28720</t>
+          <t>27583</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1652841</t>
+          <t>1662148</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2174712</t>
+          <t>2206120</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1439711</t>
+          <t>1427957</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1941329</t>
+          <t>1987130</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3130500</t>
+          <t>3131068</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3912191</t>
+          <t>3886811</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,07%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>841815</t>
+          <t>845112</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1224704</t>
+          <t>1221126</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1141675</t>
+          <t>1159557</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1527534</t>
+          <t>1533816</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2182278</t>
+          <t>2164132</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2709389</t>
+          <t>2719120</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>288837</t>
+          <t>286939</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>422251</t>
+          <t>416443</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>423038</t>
+          <t>413013</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>568716</t>
+          <t>569138</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>770113</t>
+          <t>786547</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>963131</t>
+          <t>966288</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>53532</t>
+          <t>52794</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>94836</t>
+          <t>92079</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>58566</t>
+          <t>58739</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>89883</t>
+          <t>90722</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>124107</t>
+          <t>121536</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>175163</t>
+          <t>174066</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57B2_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>249729</t>
+          <t>277633</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>226003</t>
+          <t>253571</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>271724</t>
+          <t>302855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>225548</t>
+          <t>244046</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>207962</t>
+          <t>225773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>243965</t>
+          <t>264387</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>475277</t>
+          <t>521678</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>444147</t>
+          <t>488881</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>503593</t>
+          <t>552876</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>195533</t>
+          <t>207655</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173173</t>
+          <t>184070</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>217951</t>
+          <t>230538</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,67 +873,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>173771</t>
+          <t>188202</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>157384</t>
+          <t>171481</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191820</t>
+          <t>207408</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>35,16%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>42,53%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>395857</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>364993</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>427289</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>35,22%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>42,93%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>369305</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>342943</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>401023</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>38,86%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>36,09%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48824</t>
+          <t>53466</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37443</t>
+          <t>40373</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65080</t>
+          <t>71389</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38505</t>
+          <t>45552</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29500</t>
+          <t>33787</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49970</t>
+          <t>57827</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>87328</t>
+          <t>99018</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72118</t>
+          <t>82327</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>105838</t>
+          <t>120137</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17467</t>
+          <t>20147</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>17271</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18402</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30419</t>
+          <t>30490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>503441</t>
+          <t>548636</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>503441</t>
+          <t>548636</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503441</t>
+          <t>548636</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>446872</t>
+          <t>487723</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>446872</t>
+          <t>487723</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>446872</t>
+          <t>487723</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>950313</t>
+          <t>1036358</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>950313</t>
+          <t>1036358</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>950313</t>
+          <t>1036358</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>230959</t>
+          <t>249330</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>208178</t>
+          <t>228675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>252997</t>
+          <t>272577</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>165897</t>
+          <t>187866</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>151011</t>
+          <t>169902</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>183526</t>
+          <t>206057</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>396856</t>
+          <t>437195</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>368926</t>
+          <t>406850</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>425134</t>
+          <t>467420</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,61%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>167130</t>
+          <t>177383</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147768</t>
+          <t>157198</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189414</t>
+          <t>199886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>164579</t>
+          <t>176997</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>148932</t>
+          <t>159700</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>181424</t>
+          <t>194793</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>331709</t>
+          <t>354379</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>304312</t>
+          <t>325292</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>358335</t>
+          <t>381990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,17%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47151</t>
+          <t>49205</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35334</t>
+          <t>35853</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63044</t>
+          <t>63314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47265</t>
+          <t>52553</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37751</t>
+          <t>41881</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59746</t>
+          <t>65556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>94416</t>
+          <t>101758</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78357</t>
+          <t>84781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113546</t>
+          <t>122384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12609</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11195</t>
+          <t>12421</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>20341</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>451596</t>
+          <t>482611</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>451596</t>
+          <t>482611</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>451596</t>
+          <t>482611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834176</t>
+          <t>905753</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834176</t>
+          <t>905753</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834176</t>
+          <t>905753</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>459782</t>
+          <t>239285</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>329674</t>
+          <t>217077</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>586158</t>
+          <t>262175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>76667</t>
+          <t>86869</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66727</t>
+          <t>74634</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86139</t>
+          <t>98094</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>536449</t>
+          <t>326155</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>404717</t>
+          <t>299908</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>710560</t>
+          <t>350536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>53,29%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>157107</t>
+          <t>176497</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60366</t>
+          <t>158425</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>256351</t>
+          <t>200386</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59437</t>
+          <t>67166</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50550</t>
+          <t>56681</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69507</t>
+          <t>78341</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>216544</t>
+          <t>243663</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>90042</t>
+          <t>219172</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>314598</t>
+          <t>268336</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>40,79%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>40171</t>
+          <t>44366</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>33016</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69145</t>
+          <t>57211</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>26688</t>
+          <t>29182</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20503</t>
+          <t>22070</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34768</t>
+          <t>37976</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>66859</t>
+          <t>73548</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>60663</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99961</t>
+          <t>89522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24222</t>
+          <t>24027</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>667675</t>
+          <t>470907</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>667675</t>
+          <t>470907</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>667675</t>
+          <t>470907</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>834020</t>
+          <t>657836</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>834020</t>
+          <t>657836</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>834020</t>
+          <t>657836</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>490245</t>
+          <t>532315</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>455331</t>
+          <t>497410</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>529479</t>
+          <t>569796</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>538418</t>
+          <t>370790</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>411773</t>
+          <t>345455</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>761897</t>
+          <t>398724</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1028663</t>
+          <t>903105</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>900893</t>
+          <t>858977</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1366230</t>
+          <t>946324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>364068</t>
+          <t>407764</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>330393</t>
+          <t>371999</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>396642</t>
+          <t>442340</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>308374</t>
+          <t>342582</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153876</t>
+          <t>318971</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>397647</t>
+          <t>368174</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>672442</t>
+          <t>750346</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>451869</t>
+          <t>709596</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>766627</t>
+          <t>792964</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
@@ -2658,102 +2658,102 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>151552</t>
+          <t>161775</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>132788</t>
+          <t>140979</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>176227</t>
+          <t>187363</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>14,38%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>16,65%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>130526</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>113914</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>147822</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>13,26%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>17,2%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>292302</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>265551</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>320962</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
           <t>14,73%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>12,91%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>115227</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>55260</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>152840</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>11,8%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>15,65%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>266779</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>178296</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>307347</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>22884</t>
+          <t>23294</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41951</t>
+          <t>37645</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>15297</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22430</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>37491</t>
+          <t>38591</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24723</t>
+          <t>29129</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54860</t>
+          <t>54749</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1028748</t>
+          <t>1125148</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1028748</t>
+          <t>1125148</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1028748</t>
+          <t>1125148</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>976626</t>
+          <t>859195</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>976626</t>
+          <t>859195</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>976626</t>
+          <t>859195</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2005374</t>
+          <t>1984343</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2005374</t>
+          <t>1984343</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2005374</t>
+          <t>1984343</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>197479</t>
+          <t>224701</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>175020</t>
+          <t>201297</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>222915</t>
+          <t>251351</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>253047</t>
+          <t>285889</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>189673</t>
+          <t>262146</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>291674</t>
+          <t>308241</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>450527</t>
+          <t>510589</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>364220</t>
+          <t>476646</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>495333</t>
+          <t>548661</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>39,37%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>172564</t>
+          <t>214650</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>150974</t>
+          <t>189809</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>193395</t>
+          <t>239970</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>397974</t>
+          <t>339270</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>339272</t>
+          <t>314314</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>512034</t>
+          <t>366042</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>570537</t>
+          <t>553919</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>511208</t>
+          <t>519769</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>706963</t>
+          <t>588304</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>80462</t>
+          <t>100919</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65771</t>
+          <t>84203</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>97070</t>
+          <t>120531</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>163468</t>
+          <t>176521</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>126273</t>
+          <t>156688</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>192040</t>
+          <t>196120</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>243930</t>
+          <t>277441</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>199477</t>
+          <t>253574</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>275218</t>
+          <t>307145</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>21383</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>15491</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30766</t>
+          <t>35316</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>25098</t>
+          <t>27333</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17793</t>
+          <t>20316</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33575</t>
+          <t>35769</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>46482</t>
+          <t>51490</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>33932</t>
+          <t>40670</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>59974</t>
+          <t>67432</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>471888</t>
+          <t>564427</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>471888</t>
+          <t>564427</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>471888</t>
+          <t>564427</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>839588</t>
+          <t>829013</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>839588</t>
+          <t>829013</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>839588</t>
+          <t>829013</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1311476</t>
+          <t>1393440</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1311476</t>
+          <t>1393440</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1311476</t>
+          <t>1393440</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>170640</t>
+          <t>167160</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>146806</t>
+          <t>142581</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>191890</t>
+          <t>186919</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>321812</t>
+          <t>357962</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>296931</t>
+          <t>331105</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>351255</t>
+          <t>387001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>492452</t>
+          <t>525122</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>457923</t>
+          <t>486556</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>533488</t>
+          <t>562853</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>62411</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>40339</t>
+          <t>43567</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>84778</t>
+          <t>86642</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>291585</t>
+          <t>322395</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>267766</t>
+          <t>296691</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>316720</t>
+          <t>350995</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>353565</t>
+          <t>384806</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>319582</t>
+          <t>353176</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>388007</t>
+          <t>422321</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>12485</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>124306</t>
+          <t>138082</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>109392</t>
+          <t>119837</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>140003</t>
+          <t>155671</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>130495</t>
+          <t>143877</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>113259</t>
+          <t>125644</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>148502</t>
+          <t>164347</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>18205</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>26516</t>
+          <t>28396</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>19903</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>13373</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>27583</t>
+          <t>30669</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>755908</t>
+          <t>838475</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>755908</t>
+          <t>838475</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>755908</t>
+          <t>838475</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>996415</t>
+          <t>1075703</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>996415</t>
+          <t>1075703</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>996415</t>
+          <t>1075703</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1798834</t>
+          <t>1690422</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1662148</t>
+          <t>1625960</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2206120</t>
+          <t>1756999</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1581389</t>
+          <t>1533421</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1427957</t>
+          <t>1484412</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1987130</t>
+          <t>1589636</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>3380223</t>
+          <t>3223844</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3131068</t>
+          <t>3138213</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3886811</t>
+          <t>3307449</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1118383</t>
+          <t>1246360</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>845112</t>
+          <t>1180393</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1221126</t>
+          <t>1304869</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1395720</t>
+          <t>1436611</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1159557</t>
+          <t>1382723</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1533816</t>
+          <t>1486776</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>2514103</t>
+          <t>2682970</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2164132</t>
+          <t>2599616</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2719120</t>
+          <t>2758425</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>374348</t>
+          <t>415527</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>286939</t>
+          <t>378278</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>416443</t>
+          <t>452972</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>515458</t>
+          <t>572416</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>413013</t>
+          <t>535196</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>569138</t>
+          <t>610492</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>889807</t>
+          <t>987943</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>786547</t>
+          <t>932343</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>966288</t>
+          <t>1039612</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>72290</t>
+          <t>76646</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>52794</t>
+          <t>60166</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>92079</t>
+          <t>96990</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>75351</t>
+          <t>82029</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>58739</t>
+          <t>69161</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>90722</t>
+          <t>97158</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>147641</t>
+          <t>158676</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>121536</t>
+          <t>135868</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>174066</t>
+          <t>182602</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3363855</t>
+          <t>3428956</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3363855</t>
+          <t>3428956</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3363855</t>
+          <t>3428956</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3567919</t>
+          <t>3624477</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3567919</t>
+          <t>3624477</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3567919</t>
+          <t>3624477</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6931774</t>
+          <t>7053433</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6931774</t>
+          <t>7053433</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6931774</t>
+          <t>7053433</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
